--- a/math-misconceptions/sources/math_misconceptions_item_bank.xlsx
+++ b/math-misconceptions/sources/math_misconceptions_item_bank.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sources" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Misconceptions!$A$1:$N$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Misconceptions!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -49,9 +49,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="568">
-  <si>
-    <t xml:space="preserve">Misconception item bank – grades 7–9</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="750">
+  <si>
+    <t xml:space="preserve">Misconception item bank – grades 1–9</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose</t>
@@ -63,13 +63,13 @@
     <t xml:space="preserve">Created</t>
   </si>
   <si>
-    <t xml:space="preserve">20 September 2026, from the literature summary math_misconceptions_grades7-9_summary.docx and the bibliography math_misconceptions_grades7-9.bib (85 entries).</t>
+    <t xml:space="preserve">20 September 2026, from the literature summary math_misconceptions_grades7-9_summary.docx and the bibliography math_misconceptions_grades7-9.bib (85 entries). Extended with grades 1–6 rows on 30 September 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Sheets</t>
   </si>
   <si>
-    <t xml:space="preserve">Misconceptions = the catalogue (33 rows). Item bank template = where to write real items, linked to misconception IDs. Summary = counts by strand and evidence strength (formulas). Sources = references used, parsed from the .bib file.</t>
+    <t xml:space="preserve">Misconceptions = the catalogue (42 rows). Item bank template = where to write real items, linked to misconception IDs. Summary = counts by strand and evidence strength (formulas). Sources = references used, parsed from the .bib file.</t>
   </si>
   <si>
     <t xml:space="preserve">How to use</t>
@@ -114,6 +114,24 @@
     <t xml:space="preserve">No third-party item text was copied. If you seed the bank from the Eedi Kaggle dataset or the Otero et al. (2024) benchmark, check their licences first.</t>
   </si>
   <si>
+    <t xml:space="preserve">Grade band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grades (1–9) where the topic is taught according to the OPS_1-6 and OPS_7-9 files, not the ages in the study samples. Rows catalogued before September 30 are 7–9 unless the topic is taught earlier. The Finnish curriculum item column holds A12. and A36. IDs from OPS_1-6; add S-IDs from OPS_7-9 with a semicolon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added 30 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 rows for grades 1–6: NUM-09 to NUM-13, ALG-13, GEO-03, MEA-01, MEA-02 (new Measurement strand). Existing rows were mapped to A12./A36. IDs only where a primary counterpart clearly exists (ALG-06, NUM-01 to NUM-05, GEO-01, GEO-02, PRO-03, PRO-04). NUM-10, GEO-03 and MEA-02 are Limited evidence. Example wrong answers are illustrative. Sources added to the Sources sheet. Evidence check the same day: NUM-10 raised to Moderate and its item changed to 453 − 127 (a study-recommended item type), GEO-03 reworded, MEA-01 gained a second source, MEA-02 stays Limited (no study located), NUM-13 added, NUM-03 gained a Finnish source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPERT REVIEW REQUIRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not legal advice. Using items from this bank with pupils in grades 1–6 must not involve collecting or storing data about the pupils, or sending their input to a third-party or AI service, until a data protection officer, legal counsel and a research ethics committee have reviewed and signed off (docs/privacy/expert_review_signoff_template.md). Use synthetic data until then.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
@@ -156,6 +174,9 @@
     <t xml:space="preserve">Finnish curriculum item (fill in)</t>
   </si>
   <si>
+    <t xml:space="preserve">Grade band (curriculum)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALG-01</t>
   </si>
   <si>
@@ -195,6 +216,9 @@
     <t xml:space="preserve">Algebra and equations</t>
   </si>
   <si>
+    <t xml:space="preserve">7–9</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALG-02</t>
   </si>
   <si>
@@ -342,6 +366,12 @@
     <t xml:space="preserve">kieran1981equality; knuth2006equal</t>
   </si>
   <si>
+    <t xml:space="preserve">A12.S2.08; A36.S3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–9</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALG-07</t>
   </si>
   <si>
@@ -543,6 +573,12 @@
     <t xml:space="preserve">Numbers and percentages</t>
   </si>
   <si>
+    <t xml:space="preserve">A36.S2.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–9</t>
+  </si>
+  <si>
     <t xml:space="preserve">NUM-02</t>
   </si>
   <si>
@@ -591,10 +627,13 @@
     <t xml:space="preserve">Numerator and denominator are treated as independent whole numbers.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviews and studies across grades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ni2005whole; siegler2017hard</t>
+    <t xml:space="preserve">Reviews and studies across grades Finnish sample: students with a natural-number-bias profile (n = 38; Van Hoof et al., 2025).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ni2005whole; siegler2017hard; vanhoof2025anxiety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S2.12</t>
   </si>
   <si>
     <t xml:space="preserve">NUM-04</t>
@@ -627,6 +666,9 @@
     <t xml:space="preserve">siegler2015conceptual; siegler2017hard</t>
   </si>
   <si>
+    <t xml:space="preserve">A36.S2.14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NUM-05</t>
   </si>
   <si>
@@ -651,6 +693,9 @@
     <t xml:space="preserve">Middle-school students and pre-service teachers (direction-of-effect tasks)</t>
   </si>
   <si>
+    <t xml:space="preserve">A36.S2.07; A36.S2.14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NUM-06</t>
   </si>
   <si>
@@ -825,6 +870,12 @@
     <t xml:space="preserve">tirosh1999intuitive; stavy2000how; awawdehshahbari2021cognitive</t>
   </si>
   <si>
+    <t xml:space="preserve">A36.S4.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–9</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRO-04</t>
   </si>
   <si>
@@ -885,6 +936,9 @@
     <t xml:space="preserve">fujita2007learners; silfverberg1999geometrisen; silfverberg2019geometrical</t>
   </si>
   <si>
+    <t xml:space="preserve">A36.S4.03</t>
+  </si>
+  <si>
     <t xml:space="preserve">GEO-02</t>
   </si>
   <si>
@@ -1122,6 +1176,309 @@
     <t xml:space="preserve">An intuitive rule: more of one quantity (black marbles) means more of another (chance).</t>
   </si>
   <si>
+    <t xml:space="preserve">NUM-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-digit number read as separate digits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A number such as 706 is handled as single digits placed side by side, so the value of a digit does not depend on its place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the number 706, what is the value of the digit 7?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700 (seven hundreds).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The digit is read by its face value; tens, hundreds and ones are not treated as units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceptual structures for multidigit numbers described across four teaching projects (grades 1–3); sample sizes not read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuson1997children</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A12.S2.06; A36.S2.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUM-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written subtraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smaller digit subtracted from larger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When the top digit in a column is smaller, the smaller digit is subtracted from the larger one, so no regrouping takes place. Two related variants: the next digit is also reduced by one, or regrouping is done but the next digit is not reduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate 453 − 127.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334 (3 − 7 taken as 7 − 3). Related wrong answers: 324 and 336.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regrouping across a zero is avoided by reversing the subtraction in the column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264 third-graders in 12 Dutch schools (Vermeulen et al., 2020); the error is described there as frequent across contexts (Brown &amp; VanLehn, 1980, and later studies). Multiple-choice distractors raised the error rate, so use typed answers for diagnosis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vermeulen2020evaluating; brown1980repair; hennessy1993stability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S2.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUM-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplication and division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrong operation when the multiplier is below 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplication is seen only as repeated addition of equal groups, so a multiplier below 1 seems to call for division.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One metre of ribbon costs 4 €. Which calculation gives the price of 0,5 m?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 0,5 = 2 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 : 0,5 = 8 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A repeated-addition model needs a whole-number multiplier; with 0,5 the situation no longer fits it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grades 5, 7 and 9 (Fischbein et al., 1985); longitudinal study of grades 2–3 (Mulligan &amp; Mitchelmore, 1997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fischbein1985role; mulligan1997young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A12.S2.12; A36.S2.05; A36.S2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUM-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larger denominator means larger fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-number ordering is applied to the numerator and denominator separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is larger: 1/4 or 1/8?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The denominator 8 is larger than 4, so the fraction is read as larger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural number bias reviewed by Ni &amp; Zhou (2005); its development through primary and secondary education (Van Hoof et al., 2015); middle-school students and pre-service teachers (Siegler &amp; Lortie-Forgues, 2015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ni2005whole; vanhoof2015inappropriately; siegler2015conceptual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S2.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equal sign must come at the end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An equation is only accepted in the form "operation = answer".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True or false: 8 = 5 + 3?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False, the answer must come after the equal sign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"=" is read as "the answer comes next", so an operation on the right side looks wrong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Children aged 7–11 at two US sites (McNeil &amp; Alibali, 2005); Kieran (1981)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcneil2005change; kieran1981equality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle size read from arm length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The drawn length of the arms is confused with the amount of opening between them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle A is 40° and has long arms. Angle B is 60° and has short arms. Which angle is larger?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle B (60°).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle A, because its arms are longer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The opening is the least salient feature of the angle; the arms are what is seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angle concept development in 192 children, grades 2–8 (Mitchelmore &amp; White, 2000): identifying the two arms is the main difficulty. A grade 3–4 teaching study (White &amp; Mitchelmore) found the opening least salient; arm length as a distractor is one classroom episode, not a measured rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mitchelmore2000development; whitemitchelmore_pme_angles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S4.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rectangle covering not seen as rows and columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of unit squares is built by adding the sides or by counting single squares, not by multiplying rows by columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A rectangle is covered with 1 cm × 1 cm squares in 3 rows of 5 squares. How many squares are there?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (3 + 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The row-and-column structure of the array is not seen, so the two numbers are added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115 children in grades 1–4 solving covering tasks (Outhred &amp; Mitchelmore, 2000); 445 sixth graders, with "area = length + width" among the errors shown (Tan Sisman &amp; Aksu, 2016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outhred2000young; sisman2016study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geometry and measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area units converted with the linear factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The conversion factor between length units is applied unchanged to area units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many square centimetres are in one square metre?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 000 cm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 cm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 m = 100 cm is carried over to m² and cm².</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No study located. The error is described in revision guides and in the OPS_7-9 misconception list; treat it as a teacher-reported pattern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none located</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S4.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5–6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUM-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplying by 10 taken as adding a zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A shortcut rule is applied to the written digits without place-value understanding, so it fails with decimals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate 3,5 × 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Add a zero" is applied to the written digits; the digits are not seen as moving one place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530 children aged 10–11 in Australia, New Zealand and the UK: 38–62 % correct on four items, few correct explanations, most said "a zero is added" (Hurst &amp; Hurrell, 2020); the wrong answer 3,50 is illustrative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hurst2020pseudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A36.S2.01; A36.S2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Counts by strand and evidence strength</t>
   </si>
   <si>
@@ -1134,7 +1491,7 @@
     <t xml:space="preserve">Check: total matches</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: 'Proportion and geometry' holds scaling and area/perimeter items; 'Geometry' holds shape-definition items.</t>
+    <t xml:space="preserve">Note: 'Proportion and geometry' holds scaling and area/perimeter items; 'Geometry' holds shape-definition and angle items; 'Measurement' holds unit and area-measurement items added for grades 1–6.</t>
   </si>
   <si>
     <t xml:space="preserve">Item ID</t>
@@ -1260,6 +1617,21 @@
     <t xml:space="preserve">https://doi.org/10.7771/1932-6246.1161</t>
   </si>
   <si>
+    <t xml:space="preserve">brown1980repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown &amp; VanLehn (1980)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Theory: A Generative Theory of Bugs in Procedural Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognitive Science, 4(4), 379–426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1207/s15516709cog0404_3 (abstract read; multidigit subtraction bug database)</t>
+  </si>
+  <si>
     <t xml:space="preserve">bush2013prerequisite</t>
   </si>
   <si>
@@ -1332,6 +1704,21 @@
     <t xml:space="preserve">https://doi.org/10.1023/A:1021205413749</t>
   </si>
   <si>
+    <t xml:space="preserve">fischbein1985role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischbein et al. (1985)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Role of Implicit Models in Solving Verbal Problems in Multiplication and Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal for Research in Mathematics Education, 16(1), 3–17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference confirmed in several citing works; article not read.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fischbein &amp; Schnarch (1997)</t>
   </si>
   <si>
@@ -1371,6 +1758,18 @@
     <t xml:space="preserve">https://doi.org/10.1016/j.jmathb.2011.08.003</t>
   </si>
   <si>
+    <t xml:space="preserve">Fuson et al. (1997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Children's Conceptual Structures for Multidigit Numbers and Methods of Multidigit Addition and Subtraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal for Research in Mathematics Education, 28(2), 130–162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract read: https://nctm.org/Publications/journal-for-research-in-mathematics-education/1997/Vol28/Issue2/Children_s-Conceptual-Structures-for-Multidigit-Numbers-and-Methods-of-Multidigit-Addition-and-Subtraction | DOI 10.5951/jresematheduc.28.2.0130 (from a citing reference list)</t>
+  </si>
+  <si>
     <t xml:space="preserve">heinze2002quadrat</t>
   </si>
   <si>
@@ -1386,6 +1785,33 @@
     <t xml:space="preserve">https://doi.org/10.1007/BF02655704</t>
   </si>
   <si>
+    <t xml:space="preserve">hennessy1993stability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hennessy (1993)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Stability of Children's Mathematical Behavior: When Is a Bug Really a Bug?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning and Instruction, 3, 315–338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI 10.1016/0959-4752(93)90022-R from Vermeulen et al. (2020) reference list; not read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurst &amp; Hurrell (2020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicative Thinking: 'Pseudo-Procedures' Are the Enemies of Conceptual Understanding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Electronic Journal of Mathematics Education, 15(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract read (researchonline.nd.edu.au). A 2025 review cites it as 15(2), which appears to be wrong.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Joutsenlahti &amp; Perkkilä (2024)</t>
   </si>
   <si>
@@ -1494,6 +1920,21 @@
     <t xml:space="preserve">In Intelligent Tutoring Systems, ed. Sleeman; Brown, 25–50</t>
   </si>
   <si>
+    <t xml:space="preserve">mcneil2005change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McNeil &amp; Alibali (2005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why Won't You Change Your Mind? Knowledge of Operational Patterns Hinders Learning and Performance on Equations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child Development, 76, 883–899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference confirmed in several citing works; findings (ages 7–11, decline from 7 to 9) read in a press summary, not the article.</t>
+  </si>
+  <si>
     <t xml:space="preserve">merenluoto2004number</t>
   </si>
   <si>
@@ -1509,6 +1950,36 @@
     <t xml:space="preserve">https://doi.org/10.1016/j.learninstruc.2004.06.016</t>
   </si>
   <si>
+    <t xml:space="preserve">mitchelmore2000development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchelmore &amp; White (2000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of Angle Concepts by Progressive Abstraction and Generalisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational Studies in Mathematics, 41(3), 209–238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the original .bib; abstract read (192 children, grades 2–8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mulligan1997young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulligan &amp; Mitchelmore (1997)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Children's Intuitive Models of Multiplication and Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal for Research in Mathematics Education, 28(3), 309–330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction read (nctm.org PDF); title recalled.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ni2005whole</t>
   </si>
   <si>
@@ -1524,6 +1995,21 @@
     <t xml:space="preserve">https://doi.org/10.1207/s15326985ep4001_3</t>
   </si>
   <si>
+    <t xml:space="preserve">outhred2000young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outhred &amp; Mitchelmore (2000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Children's Intuitive Understanding of Rectangular Area Measurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal for Research in Mathematics Education, 31(2), 144–167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.2307/749749 (abstract read)</t>
+  </si>
+  <si>
     <t xml:space="preserve">planinic2012comparison</t>
   </si>
   <si>
@@ -1614,6 +2100,21 @@
     <t xml:space="preserve">https://doi.org/10.1007/978-3-319-97148-3_36</t>
   </si>
   <si>
+    <t xml:space="preserve">sisman2016study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tan Sisman &amp; Aksu (2016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Study on Sixth Grade Students' Misconceptions and Errors in Spatial Measurement: Length, Area, and Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Science and Mathematics Education, 14(7), 1293–1319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s10763-015-9642-5 (abstract read; 445 sixth graders, Ankara)</t>
+  </si>
+  <si>
     <t xml:space="preserve">stavy2000how</t>
   </si>
   <si>
@@ -1716,6 +2217,36 @@
     <t xml:space="preserve">https://doi.org/10.1007/s10649-015-9613-3</t>
   </si>
   <si>
+    <t xml:space="preserve">vanhoof2025anxiety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van Hoof et al. (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Anxiety Grows With Knowledge: The Role of the Natural Number Bias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Numerical Cognition, 11, e14075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.5964/jnc.14075 (abstract read; University of Turku authors; grade not read)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vermeulen2020evaluating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vermeulen et al. (2020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluating the Characteristics of Diagnostic Items for Bridging Errors in Multi-Digit Subtraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontiers in Education, 5, 537531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.3389/feduc.2020.537531 (full text read; 264 Dutch third-graders)</t>
+  </si>
+  <si>
     <t xml:space="preserve">vinner1989images</t>
   </si>
   <si>
@@ -1740,6 +2271,21 @@
     <t xml:space="preserve">https://doi.org/10.1016/j.learninstruc.2004.06.012</t>
   </si>
   <si>
+    <t xml:space="preserve">whitemitchelmore_pme_angles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White &amp; Mitchelmore (year not shown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teaching Angles by Abstraction from Physical Activities with Concrete Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PME proceedings, vol. 4, pp. 403–410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIC ED501155; full text read (25 grade 3–4 classrooms). Year not shown in the text read.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zaslavsky et al. (2002)</t>
   </si>
   <si>
@@ -1752,7 +2298,7 @@
     <t xml:space="preserve">https://doi.org/10.1023/A:1016093305002</t>
   </si>
   <si>
-    <t xml:space="preserve">Sources are parsed from math_misconceptions_grades7-9.bib; see that file for all 85 entries and verification notes.</t>
+    <t xml:space="preserve">Sources are parsed from math_misconceptions_grades7-9.bib; see that file for all 85 entries and verification notes. Seven sources added on 30 September 2026 for the grades 1–6 rows are in math_misconceptions_grades1-6_additions.bib.</t>
   </si>
 </sst>
 </file>
@@ -1922,59 +2468,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2283,19 +2829,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2303,7 +2849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2311,7 +2857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2319,7 +2865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -2327,7 +2873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -2335,7 +2881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
@@ -2343,7 +2889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -2351,7 +2897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -2359,7 +2905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
@@ -2367,12 +2913,36 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2391,7 +2961,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -2407,1440 +2977,1986 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="7"/>
+      <c r="O2" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="D3" s="8" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="7"/>
+      <c r="O3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="O4" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="L7" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="N7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="6" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="L9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="O9" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="7"/>
+      <c r="O10" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="7"/>
+      <c r="O11" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="O12" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="L13" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N21" s="7"/>
+      <c r="O21" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N22" s="7"/>
+      <c r="O22" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="N23" s="7"/>
+      <c r="O23" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="6" t="s">
+      <c r="D39" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N39" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="M14" s="6" t="s">
+      <c r="O39" s="6" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="C43" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="M43" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="N19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="N21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="N25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="N26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="N27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="N28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="N29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="N30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="N31" s="7"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="N32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="N33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="N34" s="7"/>
+      <c r="N43" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>475</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N34"/>
+  <autoFilter ref="A1:O43"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3858,91 +4974,91 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B4" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A4,Misconceptions!$K$2:$K$34,B$3)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A4,Misconceptions!$K$2:$K$43,B$3)</f>
+        <v>4</v>
       </c>
       <c r="C4" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A4,Misconceptions!$K$2:$K$34,C$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A4,Misconceptions!$K$2:$K$43,C$3)</f>
         <v>7</v>
       </c>
       <c r="D4" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A4,Misconceptions!$K$2:$K$34,D$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A4,Misconceptions!$K$2:$K$43,D$3)</f>
         <v>2</v>
       </c>
       <c r="E4" s="10" t="n">
         <f aca="false">SUM(B4:D4)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A5,Misconceptions!$K$2:$K$34,B$3)</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A5,Misconceptions!$K$2:$K$43,B$3)</f>
+        <v>6</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A5,Misconceptions!$K$2:$K$34,C$3)</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A5,Misconceptions!$K$2:$K$43,C$3)</f>
+        <v>6</v>
       </c>
       <c r="D5" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A5,Misconceptions!$K$2:$K$34,D$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A5,Misconceptions!$K$2:$K$43,D$3)</f>
         <v>1</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM(B5:D5)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A6,Misconceptions!$K$2:$K$34,B$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A6,Misconceptions!$K$2:$K$43,B$3)</f>
         <v>2</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A6,Misconceptions!$K$2:$K$34,C$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A6,Misconceptions!$K$2:$K$43,C$3)</f>
         <v>2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A6,Misconceptions!$K$2:$K$34,D$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A6,Misconceptions!$K$2:$K$43,D$3)</f>
         <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
@@ -3950,41 +5066,41 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A7,Misconceptions!$K$2:$K$34,B$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A7,Misconceptions!$K$2:$K$43,B$3)</f>
         <v>0</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A7,Misconceptions!$K$2:$K$34,C$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A7,Misconceptions!$K$2:$K$43,C$3)</f>
         <v>2</v>
       </c>
       <c r="D7" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A7,Misconceptions!$K$2:$K$34,D$3)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A7,Misconceptions!$K$2:$K$43,D$3)</f>
+        <v>1</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B8" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A8,Misconceptions!$K$2:$K$34,B$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A8,Misconceptions!$K$2:$K$43,B$3)</f>
         <v>1</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A8,Misconceptions!$K$2:$K$34,C$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A8,Misconceptions!$K$2:$K$43,C$3)</f>
         <v>1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A8,Misconceptions!$K$2:$K$34,D$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A8,Misconceptions!$K$2:$K$43,D$3)</f>
         <v>3</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -3992,20 +5108,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A9,Misconceptions!$K$2:$K$34,B$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A9,Misconceptions!$K$2:$K$43,B$3)</f>
         <v>0</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A9,Misconceptions!$K$2:$K$34,C$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A9,Misconceptions!$K$2:$K$43,C$3)</f>
         <v>2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$34,$A9,Misconceptions!$K$2:$K$34,D$3)</f>
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A9,Misconceptions!$K$2:$K$43,D$3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -4013,48 +5129,71 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <f aca="false">SUM(B4:B9)</f>
-        <v>11</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <f aca="false">SUM(C4:C9)</f>
-        <v>16</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <f aca="false">SUM(D4:D9)</f>
-        <v>6</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <f aca="false">SUM(E4:E9)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <f aca="false">COUNTA(Misconceptions!$A$2:$A$34)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A10,Misconceptions!$K$2:$K$43,B$3)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A10,Misconceptions!$K$2:$K$43,C$3)</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">COUNTIFS(Misconceptions!$B$2:$B$43,$A10,Misconceptions!$K$2:$K$43,D$3)</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <f aca="false">SUM(B10:D10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <f aca="false">SUM(B4:B10)</f>
+        <v>13</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <f aca="false">SUM(C4:C10)</f>
+        <v>21</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <f aca="false">SUM(D4:D10)</f>
+        <v>8</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <f aca="false">SUM(E4:E10)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E13" s="13" t="str">
-        <f aca="false">IF(E10=E12,"OK","CHECK")</f>
+        <v>478</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <f aca="false">COUNTA(Misconceptions!$A$2:$A$43)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E14" s="13" t="str">
+        <f aca="false">IF(E11=E13,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>361</v>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -4089,88 +5228,88 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="36"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>362</v>
+        <v>481</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>363</v>
+        <v>482</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>364</v>
+        <v>483</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>365</v>
+        <v>484</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>366</v>
+        <v>485</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>367</v>
+        <v>486</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>369</v>
+        <v>488</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>371</v>
+        <v>490</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>373</v>
+        <v>492</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C2" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B2,Misconceptions!$A$2:$A$34,0)),"")</f>
+        <f aca="false">IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B2,Misconceptions!$A$2:$A$43,0)),"")</f>
         <v>Operational reading of '='</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>374</v>
+        <v>493</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>375</v>
+        <v>494</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>376</v>
+        <v>495</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>377</v>
+        <v>496</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>378</v>
+        <v>497</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>379</v>
+        <v>498</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="6" t="str">
-        <f aca="false">IF($B3="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B3,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B3="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B3,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D3" s="7"/>
@@ -4183,11 +5322,11 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6" t="str">
-        <f aca="false">IF($B4="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B4,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B4="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B4,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D4" s="7"/>
@@ -4200,11 +5339,11 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6" t="str">
-        <f aca="false">IF($B5="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B5,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B5="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B5,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D5" s="7"/>
@@ -4217,11 +5356,11 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="6" t="str">
-        <f aca="false">IF($B6="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B6,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B6="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B6,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D6" s="7"/>
@@ -4234,11 +5373,11 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="6" t="str">
-        <f aca="false">IF($B7="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B7,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B7="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B7,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D7" s="7"/>
@@ -4251,11 +5390,11 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="6" t="str">
-        <f aca="false">IF($B8="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B8,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B8="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B8,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D8" s="7"/>
@@ -4268,11 +5407,11 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="6" t="str">
-        <f aca="false">IF($B9="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B9,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B9="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B9,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D9" s="7"/>
@@ -4285,11 +5424,11 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6" t="str">
-        <f aca="false">IF($B10="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B10,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B10="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B10,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D10" s="7"/>
@@ -4302,11 +5441,11 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6" t="str">
-        <f aca="false">IF($B11="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B11,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B11="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B11,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D11" s="7"/>
@@ -4319,11 +5458,11 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6" t="str">
-        <f aca="false">IF($B12="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B12,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B12="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B12,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D12" s="7"/>
@@ -4336,11 +5475,11 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6" t="str">
-        <f aca="false">IF($B13="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B13,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B13="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B13,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D13" s="7"/>
@@ -4353,11 +5492,11 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="6" t="str">
-        <f aca="false">IF($B14="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B14,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B14="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B14,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D14" s="7"/>
@@ -4370,11 +5509,11 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6" t="str">
-        <f aca="false">IF($B15="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B15,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B15="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B15,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D15" s="7"/>
@@ -4387,11 +5526,11 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6" t="str">
-        <f aca="false">IF($B16="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B16,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B16="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B16,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D16" s="7"/>
@@ -4404,11 +5543,11 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6" t="str">
-        <f aca="false">IF($B17="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B17,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B17="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B17,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D17" s="7"/>
@@ -4421,11 +5560,11 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6" t="str">
-        <f aca="false">IF($B18="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B18,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B18="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B18,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D18" s="7"/>
@@ -4438,11 +5577,11 @@
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6" t="str">
-        <f aca="false">IF($B19="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B19,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B19="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B19,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D19" s="7"/>
@@ -4455,11 +5594,11 @@
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6" t="str">
-        <f aca="false">IF($B20="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B20,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B20="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B20,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D20" s="7"/>
@@ -4472,11 +5611,11 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6" t="str">
-        <f aca="false">IF($B21="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B21,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B21="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B21,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D21" s="7"/>
@@ -4489,11 +5628,11 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6" t="str">
-        <f aca="false">IF($B22="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B22,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B22="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B22,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D22" s="7"/>
@@ -4506,11 +5645,11 @@
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6" t="str">
-        <f aca="false">IF($B23="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B23,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B23="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B23,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D23" s="7"/>
@@ -4523,11 +5662,11 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6" t="str">
-        <f aca="false">IF($B24="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B24,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B24="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B24,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D24" s="7"/>
@@ -4540,11 +5679,11 @@
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="6" t="str">
-        <f aca="false">IF($B25="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B25,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B25="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B25,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D25" s="7"/>
@@ -4557,11 +5696,11 @@
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6" t="str">
-        <f aca="false">IF($B26="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B26,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B26="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B26,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D26" s="7"/>
@@ -4574,11 +5713,11 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6" t="str">
-        <f aca="false">IF($B27="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B27,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B27="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B27,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D27" s="7"/>
@@ -4591,11 +5730,11 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6" t="str">
-        <f aca="false">IF($B28="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B28,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B28="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B28,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D28" s="7"/>
@@ -4608,11 +5747,11 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6" t="str">
-        <f aca="false">IF($B29="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B29,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B29="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B29,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D29" s="7"/>
@@ -4625,11 +5764,11 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6" t="str">
-        <f aca="false">IF($B30="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B30,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B30="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B30,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D30" s="7"/>
@@ -4642,11 +5781,11 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6" t="str">
-        <f aca="false">IF($B31="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B31,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B31="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B31,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D31" s="7"/>
@@ -4659,11 +5798,11 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6" t="str">
-        <f aca="false">IF($B32="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B32,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B32="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B32,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D32" s="7"/>
@@ -4676,11 +5815,11 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6" t="str">
-        <f aca="false">IF($B33="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B33,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B33="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B33,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D33" s="7"/>
@@ -4693,11 +5832,11 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6" t="str">
-        <f aca="false">IF($B34="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B34,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B34="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B34,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D34" s="7"/>
@@ -4710,11 +5849,11 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="6" t="str">
-        <f aca="false">IF($B35="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B35,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B35="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B35,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D35" s="7"/>
@@ -4727,11 +5866,11 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="6" t="str">
-        <f aca="false">IF($B36="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B36,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B36="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B36,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D36" s="7"/>
@@ -4744,11 +5883,11 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="6" t="str">
-        <f aca="false">IF($B37="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B37,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B37="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B37,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D37" s="7"/>
@@ -4761,11 +5900,11 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="6" t="str">
-        <f aca="false">IF($B38="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B38,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B38="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B38,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D38" s="7"/>
@@ -4778,11 +5917,11 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6" t="str">
-        <f aca="false">IF($B39="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B39,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B39="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B39,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D39" s="7"/>
@@ -4795,11 +5934,11 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="6" t="str">
-        <f aca="false">IF($B40="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B40,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B40="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B40,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D40" s="7"/>
@@ -4812,11 +5951,11 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="6" t="str">
-        <f aca="false">IF($B41="","",IFERROR(INDEX(Misconceptions!$D$2:$D$34,MATCH($B41,Misconceptions!$A$2:$A$34,0)),"ID not found"))</f>
+        <f aca="false">IF($B41="","",IFERROR(INDEX(Misconceptions!$D$2:$D$43,MATCH($B41,Misconceptions!$A$2:$A$43,0)),"ID not found"))</f>
         <v/>
       </c>
       <c r="D41" s="7"/>
@@ -4829,15 +5968,15 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>381</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Choose an ID from the Misconceptions sheet." errorStyle="stop" errorTitle="Unknown misconception ID" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B41" type="list">
-      <formula1>Misconceptions!$A$2:$A$34</formula1>
+      <formula1>Misconceptions!$A$2:$A$43</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J41" type="list">
@@ -4860,7 +5999,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="30"/>
@@ -4870,843 +6009,1116 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>382</v>
+        <v>501</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>383</v>
+        <v>502</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A2&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A3&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A4&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A5&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A6&amp;"*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A7&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A8&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A9&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A10&amp;"*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A11&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A12&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A13&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A14&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A2&amp;"*")</f>
+      <c r="B15" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A15&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A3&amp;"*")</f>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A16&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A17&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A18&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A19&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A4&amp;"*")</f>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A20&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A21&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A5&amp;"*")</f>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A22&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A23&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A24&amp;"*")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A25&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A26&amp;"*")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A27&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A28&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A29&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A30&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A31&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A32&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A33&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A34&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A35&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A36&amp;"*")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A6&amp;"*")</f>
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A37&amp;"*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A38&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A7&amp;"*")</f>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A39&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A8&amp;"*")</f>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A40&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A41&amp;"*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A42&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A43&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A9&amp;"*")</f>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A44&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A45&amp;"*")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A10&amp;"*")</f>
+    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A46&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A11&amp;"*")</f>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A47&amp;"*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A48&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A12&amp;"*")</f>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A49&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A13&amp;"*")</f>
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A50&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A14&amp;"*")</f>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A51&amp;"*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A52&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A15&amp;"*")</f>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A53&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A16&amp;"*")</f>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$43,"*"&amp;A54&amp;"*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A17&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A18&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A19&amp;"*")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A20&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A21&amp;"*")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A22&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A23&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A24&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A25&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A26&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A27&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A28&amp;"*")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A29&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A30&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A31&amp;"*")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A32&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A33&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A34&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A35&amp;"*")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A36&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A37&amp;"*")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>551</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A38&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A39&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A40&amp;"*")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <f aca="false">COUNTIF(Misconceptions!$L$2:$L$34,"*"&amp;A41&amp;"*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="s">
-        <v>567</v>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
+        <v>749</v>
       </c>
     </row>
   </sheetData>
